--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>No</t>
   </si>
@@ -47,6 +47,12 @@
   </si>
   <si>
     <t>Dia</t>
+  </si>
+  <si>
+    <t>Bugfix</t>
+  </si>
+  <si>
+    <t>Perbaikan</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -446,6 +452,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>No</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Perbaikan</t>
+  </si>
+  <si>
+    <t>bugfix002</t>
+  </si>
+  <si>
+    <t>Perbaikan 002</t>
   </si>
 </sst>
 </file>
@@ -394,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -463,6 +469,17 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>No</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Perbaikan</t>
+  </si>
+  <si>
+    <t>Bugfix003</t>
+  </si>
+  <si>
+    <t>Perbaikan 003</t>
   </si>
 </sst>
 </file>
@@ -394,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -463,6 +469,17 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>No</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>Perbaikan 003</t>
+  </si>
+  <si>
+    <t>bugfix004</t>
+  </si>
+  <si>
+    <t>Perbaikan 004</t>
   </si>
 </sst>
 </file>
@@ -406,8 +412,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -497,6 +506,17 @@
         <v>16</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>No</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>Perbaikan 003</t>
+  </si>
+  <si>
+    <t>bugfix005</t>
+  </si>
+  <si>
+    <t>Perbaikan 005</t>
   </si>
 </sst>
 </file>
@@ -406,8 +412,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -497,6 +506,17 @@
         <v>16</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
